--- a/public/dashboard.xlsx
+++ b/public/dashboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="7"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Toelichting" sheetId="1" state="visible" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Je kunt zelf maatwerkplannen toevoegen aan dit excel-bestand met deze tool:</t>
   </si>
   <si>
-    <t>https://mwpbn.madebymark.nl</t>
+    <t>https://mwpbn.web.app</t>
   </si>
   <si>
     <t xml:space="preserve">Let op!</t>
@@ -1591,7 +1591,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="C6" tooltip=""/>
+    <hyperlink r:id="rId1" ref="C6"/>
     <hyperlink location="Dashboard!A1" ref="C12" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
@@ -3739,7 +3739,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="4" operator="equal" id="{00B8009A-003F-410F-9AEC-0035003C00F8}">
+          <x14:cfRule type="expression" priority="4" operator="equal" id="{00ED00BA-0002-4F52-8808-00D600AC0048}">
             <xm:f>H4=0</xm:f>
             <x14:dxf>
               <font>
@@ -3756,7 +3756,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="3" operator="equal" id="{000C00AA-00C7-43F9-996D-00F100A20003}">
+          <x14:cfRule type="expression" priority="3" operator="equal" id="{003B0034-000B-4A14-9422-008400EE0034}">
             <xm:f>H4=1</xm:f>
             <x14:dxf>
               <font>
@@ -3773,7 +3773,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" operator="equal" id="{00C2001B-0076-4CF8-B5F5-0015006D00F8}">
+          <x14:cfRule type="expression" priority="2" operator="equal" id="{001D00B0-0075-4406-9FD9-00C500A0008B}">
             <xm:f>H4=2</xm:f>
             <x14:dxf>
               <font>
@@ -3790,7 +3790,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" operator="equal" id="{00B60078-0047-4FE2-9B6E-002C00ED003C}">
+          <x14:cfRule type="expression" priority="1" operator="equal" id="{002B00CD-0035-4703-BF62-00B100E5006D}">
             <xm:f>H4=3</xm:f>
             <x14:dxf>
               <font>
@@ -11433,7 +11433,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="4" operator="equal" id="{001B0031-00EB-4052-A4CA-006200E900B9}">
+          <x14:cfRule type="expression" priority="4" operator="equal" id="{00A300A4-00C3-4CB7-9C5B-00940024008E}">
             <xm:f>H4=0</xm:f>
             <x14:dxf>
               <font>
@@ -11450,7 +11450,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="3" operator="equal" id="{00F4001B-0046-4026-9D96-0009001C005A}">
+          <x14:cfRule type="expression" priority="3" operator="equal" id="{00E7003D-009D-4723-9842-006E008700B3}">
             <xm:f>H4=1</xm:f>
             <x14:dxf>
               <font>
@@ -11467,7 +11467,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" operator="equal" id="{009B00EB-00EF-4E02-9270-001800B30090}">
+          <x14:cfRule type="expression" priority="2" operator="equal" id="{00FD0016-00C2-491D-BEFB-0074007D0039}">
             <xm:f>H4=2</xm:f>
             <x14:dxf>
               <font>
@@ -11484,7 +11484,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" operator="equal" id="{003E00BE-00B4-43CB-B18D-00A700D000D0}">
+          <x14:cfRule type="expression" priority="1" operator="equal" id="{000E00A3-0038-4ECD-894D-008C0039008F}">
             <xm:f>H4=3</xm:f>
             <x14:dxf>
               <font>

--- a/public/dashboard.xlsx
+++ b/public/dashboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Toelichting" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t>Toelichting</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maak hier je eigen analyse</t>
   </si>
   <si>
     <t>Nr</t>
@@ -1604,7 +1607,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" ht="15">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
@@ -1621,103 +1630,103 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="14.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" ht="14.25">
@@ -1943,17 +1952,17 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1">
         <v>1</v>
@@ -2076,7 +2085,7 @@
         <v>40</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW1" s="1">
         <v>1</v>
@@ -2201,7 +2210,7 @@
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="1"/>
@@ -2209,7 +2218,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2252,7 +2261,7 @@
       <c r="AT2" s="1"/>
       <c r="AU2" s="1"/>
       <c r="AV2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
@@ -2297,25 +2306,25 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3" s="6">
         <f>COUNTIF(H4:H45,"&gt;=2")</f>
@@ -2646,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="6">
         <f t="shared" ref="C4:C9" si="0">COUNTIF($H4:$AU4,"=0")</f>
@@ -2751,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="6">
         <f t="shared" si="0"/>
@@ -2775,7 +2784,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="6">
         <f t="shared" si="0"/>
@@ -2799,7 +2808,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="6">
         <f t="shared" si="0"/>
@@ -2823,7 +2832,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6">
         <f t="shared" si="0"/>
@@ -2847,7 +2856,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="6">
         <f t="shared" si="0"/>
@@ -2871,7 +2880,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="6">
         <f t="shared" ref="C10:C45" si="4">COUNTIF($H10:$AU10,"=0")</f>
@@ -2895,7 +2904,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="6">
         <f t="shared" si="4"/>
@@ -2919,7 +2928,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="6">
         <f t="shared" si="4"/>
@@ -2943,7 +2952,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="6">
         <f t="shared" si="4"/>
@@ -2967,7 +2976,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" s="6">
         <f t="shared" si="4"/>
@@ -2991,7 +3000,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6">
         <f t="shared" si="4"/>
@@ -3015,7 +3024,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="6">
         <f t="shared" si="4"/>
@@ -3039,7 +3048,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" s="6">
         <f t="shared" si="4"/>
@@ -3063,7 +3072,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="6">
         <f t="shared" si="4"/>
@@ -3087,7 +3096,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="6">
         <f t="shared" si="4"/>
@@ -3111,7 +3120,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="6">
         <f t="shared" si="4"/>
@@ -3135,7 +3144,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" s="6">
         <f t="shared" si="4"/>
@@ -3159,7 +3168,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="6">
         <f t="shared" si="4"/>
@@ -3183,7 +3192,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="6">
         <f t="shared" si="4"/>
@@ -3207,7 +3216,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24" s="6">
         <f t="shared" si="4"/>
@@ -3231,7 +3240,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="6">
         <f t="shared" si="4"/>
@@ -3255,7 +3264,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" s="6">
         <f t="shared" si="4"/>
@@ -3279,7 +3288,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C27" s="6">
         <f t="shared" si="4"/>
@@ -3303,7 +3312,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" s="6">
         <f t="shared" si="4"/>
@@ -3327,7 +3336,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="6">
         <f t="shared" si="4"/>
@@ -3351,7 +3360,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" s="6">
         <f t="shared" si="4"/>
@@ -3375,7 +3384,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="6">
         <f t="shared" si="4"/>
@@ -3399,7 +3408,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" s="6">
         <f t="shared" si="4"/>
@@ -3423,7 +3432,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="6">
         <f t="shared" si="4"/>
@@ -3447,7 +3456,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="6">
         <f t="shared" si="4"/>
@@ -3471,7 +3480,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="6">
         <f t="shared" si="4"/>
@@ -3495,7 +3504,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="6">
         <f t="shared" si="4"/>
@@ -3519,7 +3528,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="6">
         <f t="shared" si="4"/>
@@ -3543,7 +3552,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="6">
         <f t="shared" si="4"/>
@@ -3567,7 +3576,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="6">
         <f t="shared" si="4"/>
@@ -3591,7 +3600,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="6">
         <f t="shared" si="4"/>
@@ -3615,7 +3624,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" s="6">
         <f t="shared" si="4"/>
@@ -3639,7 +3648,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C42" s="6">
         <f t="shared" si="4"/>
@@ -3663,7 +3672,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C43" s="6">
         <f t="shared" si="4"/>
@@ -3687,7 +3696,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C44" s="6">
         <f t="shared" si="4"/>
@@ -3711,7 +3720,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C45" s="6">
         <f t="shared" si="4"/>
@@ -3739,7 +3748,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="4" operator="equal" id="{00ED00BA-0002-4F52-8808-00D600AC0048}">
+          <x14:cfRule type="expression" priority="4" operator="equal" id="{00B70027-002D-4F50-B290-00A3004A007E}">
             <xm:f>H4=0</xm:f>
             <x14:dxf>
               <font>
@@ -3756,7 +3765,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="3" operator="equal" id="{003B0034-000B-4A14-9422-008400EE0034}">
+          <x14:cfRule type="expression" priority="3" operator="equal" id="{006600DC-0021-4EE1-B707-00A800F200FE}">
             <xm:f>H4=1</xm:f>
             <x14:dxf>
               <font>
@@ -3773,7 +3782,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" operator="equal" id="{001D00B0-0075-4406-9FD9-00C500A0008B}">
+          <x14:cfRule type="expression" priority="2" operator="equal" id="{003B00D6-0055-4378-B170-00EC001C0006}">
             <xm:f>H4=2</xm:f>
             <x14:dxf>
               <font>
@@ -3790,7 +3799,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" operator="equal" id="{002B00CD-0035-4703-BF62-00B100E5006D}">
+          <x14:cfRule type="expression" priority="1" operator="equal" id="{00AA006E-0080-45AE-8A72-001000BD00C1}">
             <xm:f>H4=3</xm:f>
             <x14:dxf>
               <font>
@@ -3826,12 +3835,12 @@
   <sheetData>
     <row r="1" s="7" customFormat="1" ht="15.6" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E1" s="7">
         <v>1</v>
@@ -3954,7 +3963,7 @@
         <v>40</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW1" s="7">
         <v>1</v>
@@ -4079,16 +4088,16 @@
     </row>
     <row r="2" s="7" customFormat="1" ht="15.6" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -4131,7 +4140,7 @@
       <c r="AQ2" s="7"/>
       <c r="AR2" s="7"/>
       <c r="AV2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AW2" s="7"/>
       <c r="AX2" s="7"/>
@@ -4179,7 +4188,7 @@
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" s="7">
         <f>SUM(E4:E137)</f>
@@ -4507,13 +4516,13 @@
     </row>
     <row r="4" ht="16.800000000000001" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="10">
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <f t="shared" ref="D4:D9" si="8">SUM(E4:AR4)</f>
@@ -4522,7 +4531,7 @@
     </row>
     <row r="5" ht="16.800000000000001" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="14"/>
@@ -4574,13 +4583,13 @@
     </row>
     <row r="6" ht="16.800000000000001" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" s="16">
         <v>2</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" s="15">
         <f t="shared" si="8"/>
@@ -4589,7 +4598,7 @@
     </row>
     <row r="7" ht="16.800000000000001" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
@@ -4600,7 +4609,7 @@
     </row>
     <row r="8" ht="16.800000000000001" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="11"/>
@@ -4611,7 +4620,7 @@
     </row>
     <row r="9" ht="16.800000000000001" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="14"/>
@@ -4622,13 +4631,13 @@
     </row>
     <row r="10" ht="16.800000000000001" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B10" s="16">
         <v>3</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" ref="D10:D73" si="9">SUM(E10:AR10)</f>
@@ -4637,7 +4646,7 @@
     </row>
     <row r="11" ht="16.800000000000001" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
@@ -4648,13 +4657,13 @@
     </row>
     <row r="12" ht="16.800000000000001" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B12" s="16">
         <v>4</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="15">
         <f t="shared" si="9"/>
@@ -4663,7 +4672,7 @@
     </row>
     <row r="13" ht="16.800000000000001" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
@@ -4674,7 +4683,7 @@
     </row>
     <row r="14" ht="16.800000000000001" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
@@ -4685,7 +4694,7 @@
     </row>
     <row r="15" ht="16.800000000000001" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="14"/>
@@ -4696,13 +4705,13 @@
     </row>
     <row r="16" ht="16.800000000000001" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" s="16">
         <v>5</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="15">
         <f t="shared" si="9"/>
@@ -4711,7 +4720,7 @@
     </row>
     <row r="17" ht="16.800000000000001" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="11"/>
@@ -4722,7 +4731,7 @@
     </row>
     <row r="18" ht="16.800000000000001" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="11"/>
@@ -4733,7 +4742,7 @@
     </row>
     <row r="19" ht="16.800000000000001" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="11"/>
@@ -4744,7 +4753,7 @@
     </row>
     <row r="20" ht="16.800000000000001" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="11"/>
@@ -4755,7 +4764,7 @@
     </row>
     <row r="21" ht="16.800000000000001" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="14"/>
@@ -4766,13 +4775,13 @@
     </row>
     <row r="22" ht="16.800000000000001" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B22" s="16">
         <v>6</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" s="15">
         <f t="shared" si="9"/>
@@ -4781,7 +4790,7 @@
     </row>
     <row r="23" ht="16.800000000000001" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
@@ -4792,7 +4801,7 @@
     </row>
     <row r="24" ht="16.800000000000001" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="11"/>
@@ -4803,7 +4812,7 @@
     </row>
     <row r="25" ht="16.800000000000001" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="11"/>
@@ -4814,7 +4823,7 @@
     </row>
     <row r="26" ht="16.800000000000001" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="14"/>
@@ -4825,13 +4834,13 @@
     </row>
     <row r="27" ht="16.800000000000001" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B27" s="16">
         <v>7</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D27" s="15">
         <f t="shared" si="9"/>
@@ -4840,7 +4849,7 @@
     </row>
     <row r="28" ht="16.800000000000001" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="14"/>
@@ -4851,13 +4860,13 @@
     </row>
     <row r="29" ht="16.800000000000001" customHeight="1">
       <c r="A29" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B29" s="16">
         <v>8</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D29" s="15">
         <f t="shared" si="9"/>
@@ -4866,7 +4875,7 @@
     </row>
     <row r="30" ht="16.800000000000001" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="11"/>
@@ -4877,7 +4886,7 @@
     </row>
     <row r="31" ht="16.800000000000001" customHeight="1">
       <c r="A31" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="11"/>
@@ -4888,7 +4897,7 @@
     </row>
     <row r="32" ht="16.800000000000001" customHeight="1">
       <c r="A32" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="11"/>
@@ -4899,7 +4908,7 @@
     </row>
     <row r="33" ht="16.800000000000001" customHeight="1">
       <c r="A33" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="11"/>
@@ -4910,7 +4919,7 @@
     </row>
     <row r="34" ht="16.800000000000001" customHeight="1">
       <c r="A34" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="10"/>
       <c r="C34" s="11"/>
@@ -4921,7 +4930,7 @@
     </row>
     <row r="35" ht="16.800000000000001" customHeight="1">
       <c r="A35" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="10"/>
       <c r="C35" s="11"/>
@@ -4932,7 +4941,7 @@
     </row>
     <row r="36" ht="16.800000000000001" customHeight="1">
       <c r="A36" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
@@ -4943,7 +4952,7 @@
     </row>
     <row r="37" ht="16.800000000000001" customHeight="1">
       <c r="A37" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
@@ -4954,7 +4963,7 @@
     </row>
     <row r="38" ht="16.800000000000001" customHeight="1">
       <c r="A38" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
@@ -4965,7 +4974,7 @@
     </row>
     <row r="39" ht="16.800000000000001" customHeight="1">
       <c r="A39" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B39" s="10"/>
       <c r="C39" s="11"/>
@@ -4976,7 +4985,7 @@
     </row>
     <row r="40" ht="16.800000000000001" customHeight="1">
       <c r="A40" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="14"/>
@@ -4987,13 +4996,13 @@
     </row>
     <row r="41" ht="16.800000000000001" customHeight="1">
       <c r="A41" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B41" s="16">
         <v>9</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D41" s="15">
         <f t="shared" si="9"/>
@@ -5002,7 +5011,7 @@
     </row>
     <row r="42" ht="16.800000000000001" customHeight="1">
       <c r="A42" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
@@ -5013,7 +5022,7 @@
     </row>
     <row r="43" ht="16.800000000000001" customHeight="1">
       <c r="A43" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="14"/>
@@ -5024,13 +5033,13 @@
     </row>
     <row r="44" ht="16.800000000000001" customHeight="1">
       <c r="A44" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B44" s="16">
         <v>10</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D44" s="15">
         <f t="shared" si="9"/>
@@ -5039,7 +5048,7 @@
     </row>
     <row r="45" ht="16.800000000000001" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="9"/>
@@ -5050,13 +5059,13 @@
     </row>
     <row r="46" ht="16.800000000000001" customHeight="1">
       <c r="A46" s="21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B46" s="22">
         <v>11</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D46" s="15">
         <f t="shared" si="9"/>
@@ -5065,13 +5074,13 @@
     </row>
     <row r="47" ht="16.800000000000001" customHeight="1">
       <c r="A47" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B47" s="16">
         <v>12</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D47" s="15">
         <f t="shared" si="9"/>
@@ -5080,7 +5089,7 @@
     </row>
     <row r="48" ht="16.800000000000001" customHeight="1">
       <c r="A48" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
@@ -5091,7 +5100,7 @@
     </row>
     <row r="49" ht="16.800000000000001" customHeight="1">
       <c r="A49" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
@@ -5102,7 +5111,7 @@
     </row>
     <row r="50" ht="16.800000000000001" customHeight="1">
       <c r="A50" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
@@ -5113,7 +5122,7 @@
     </row>
     <row r="51" ht="16.800000000000001" customHeight="1">
       <c r="A51" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B51" s="13"/>
       <c r="C51" s="14"/>
@@ -5124,13 +5133,13 @@
     </row>
     <row r="52" ht="16.800000000000001" customHeight="1">
       <c r="A52" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B52" s="16">
         <v>13</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D52" s="15">
         <f t="shared" si="9"/>
@@ -5139,7 +5148,7 @@
     </row>
     <row r="53" ht="16.800000000000001" customHeight="1">
       <c r="A53" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B53" s="13"/>
       <c r="C53" s="14"/>
@@ -5150,7 +5159,7 @@
     </row>
     <row r="54" ht="16.800000000000001" customHeight="1">
       <c r="A54" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B54" s="16">
         <v>14</v>
@@ -5166,7 +5175,7 @@
     </row>
     <row r="55" ht="16.800000000000001" customHeight="1">
       <c r="A55" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
@@ -5177,7 +5186,7 @@
     </row>
     <row r="56" ht="16.800000000000001" customHeight="1">
       <c r="A56" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B56" s="13"/>
       <c r="C56" s="14"/>
@@ -5188,13 +5197,13 @@
     </row>
     <row r="57" ht="16.800000000000001" customHeight="1">
       <c r="A57" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B57" s="16">
         <v>15</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="9"/>
@@ -5203,7 +5212,7 @@
     </row>
     <row r="58" ht="16.800000000000001" customHeight="1">
       <c r="A58" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B58" s="10"/>
       <c r="C58" s="11"/>
@@ -5214,7 +5223,7 @@
     </row>
     <row r="59" ht="16.800000000000001" customHeight="1">
       <c r="A59" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B59" s="10"/>
       <c r="C59" s="11"/>
@@ -5225,7 +5234,7 @@
     </row>
     <row r="60" ht="16.800000000000001" customHeight="1">
       <c r="A60" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B60" s="10"/>
       <c r="C60" s="11"/>
@@ -5236,7 +5245,7 @@
     </row>
     <row r="61" ht="16.800000000000001" customHeight="1">
       <c r="A61" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="11"/>
@@ -5247,7 +5256,7 @@
     </row>
     <row r="62" ht="16.800000000000001" customHeight="1">
       <c r="A62" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="14"/>
@@ -5258,13 +5267,13 @@
     </row>
     <row r="63" ht="16.800000000000001" customHeight="1">
       <c r="A63" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B63" s="16">
         <v>16</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="9"/>
@@ -5273,7 +5282,7 @@
     </row>
     <row r="64" ht="16.800000000000001" customHeight="1">
       <c r="A64" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B64" s="10"/>
       <c r="C64" s="11"/>
@@ -5284,7 +5293,7 @@
     </row>
     <row r="65" ht="16.800000000000001" customHeight="1">
       <c r="A65" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B65" s="10"/>
       <c r="C65" s="11"/>
@@ -5295,7 +5304,7 @@
     </row>
     <row r="66" ht="16.800000000000001" customHeight="1">
       <c r="A66" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B66" s="13"/>
       <c r="C66" s="14"/>
@@ -5306,13 +5315,13 @@
     </row>
     <row r="67" ht="16.800000000000001" customHeight="1">
       <c r="A67" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B67" s="16">
         <v>17</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="9"/>
@@ -5321,7 +5330,7 @@
     </row>
     <row r="68" ht="16.800000000000001" customHeight="1">
       <c r="A68" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="14"/>
@@ -5332,13 +5341,13 @@
     </row>
     <row r="69" ht="16.800000000000001" customHeight="1">
       <c r="A69" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B69" s="16">
         <v>18</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="9"/>
@@ -5347,7 +5356,7 @@
     </row>
     <row r="70" ht="16.800000000000001" customHeight="1">
       <c r="A70" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="18"/>
@@ -5358,7 +5367,7 @@
     </row>
     <row r="71" ht="16.800000000000001" customHeight="1">
       <c r="A71" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B71" s="13"/>
       <c r="C71" s="18"/>
@@ -5369,13 +5378,13 @@
     </row>
     <row r="72" ht="16.800000000000001" customHeight="1">
       <c r="A72" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B72" s="16">
         <v>19</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="9"/>
@@ -5384,7 +5393,7 @@
     </row>
     <row r="73" ht="16.800000000000001" customHeight="1">
       <c r="A73" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B73" s="10"/>
       <c r="C73" s="11"/>
@@ -5395,7 +5404,7 @@
     </row>
     <row r="74" ht="16.800000000000001" customHeight="1">
       <c r="A74" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B74" s="13"/>
       <c r="C74" s="14"/>
@@ -5406,13 +5415,13 @@
     </row>
     <row r="75" ht="16.800000000000001" customHeight="1">
       <c r="A75" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B75" s="16">
         <v>20</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D75" s="15">
         <f t="shared" si="10"/>
@@ -5421,7 +5430,7 @@
     </row>
     <row r="76" ht="16.800000000000001" customHeight="1">
       <c r="A76" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B76" s="10"/>
       <c r="C76" s="11"/>
@@ -5432,7 +5441,7 @@
     </row>
     <row r="77" ht="16.800000000000001" customHeight="1">
       <c r="A77" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="11"/>
@@ -5443,7 +5452,7 @@
     </row>
     <row r="78" ht="16.800000000000001" customHeight="1">
       <c r="A78" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B78" s="10"/>
       <c r="C78" s="11"/>
@@ -5454,7 +5463,7 @@
     </row>
     <row r="79" ht="16.800000000000001" customHeight="1">
       <c r="A79" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B79" s="13"/>
       <c r="C79" s="14"/>
@@ -5465,13 +5474,13 @@
     </row>
     <row r="80" ht="16.800000000000001" customHeight="1">
       <c r="A80" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="22">
         <v>21</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D80" s="15">
         <f t="shared" si="10"/>
@@ -5480,13 +5489,13 @@
     </row>
     <row r="81" ht="16.800000000000001" customHeight="1">
       <c r="A81" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B81" s="16">
         <v>22</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D81" s="15">
         <f t="shared" si="10"/>
@@ -5495,7 +5504,7 @@
     </row>
     <row r="82" ht="16.800000000000001" customHeight="1">
       <c r="A82" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B82" s="13"/>
       <c r="C82" s="14"/>
@@ -5506,13 +5515,13 @@
     </row>
     <row r="83" ht="16.800000000000001" customHeight="1">
       <c r="A83" s="23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B83" s="22">
         <v>23</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D83" s="15">
         <f t="shared" si="10"/>
@@ -5521,13 +5530,13 @@
     </row>
     <row r="84" ht="16.800000000000001" customHeight="1">
       <c r="A84" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B84" s="16">
         <v>24</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D84" s="15">
         <f t="shared" si="10"/>
@@ -5536,7 +5545,7 @@
     </row>
     <row r="85" ht="16.800000000000001" customHeight="1">
       <c r="A85" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="11"/>
@@ -5547,7 +5556,7 @@
     </row>
     <row r="86" ht="16.800000000000001" customHeight="1">
       <c r="A86" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B86" s="13"/>
       <c r="C86" s="14"/>
@@ -5558,13 +5567,13 @@
     </row>
     <row r="87" ht="16.800000000000001" customHeight="1">
       <c r="A87" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B87" s="16">
         <v>25</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D87" s="15">
         <f t="shared" si="10"/>
@@ -5573,7 +5582,7 @@
     </row>
     <row r="88" ht="16.800000000000001" customHeight="1">
       <c r="A88" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B88" s="13"/>
       <c r="C88" s="14"/>
@@ -5584,13 +5593,13 @@
     </row>
     <row r="89" ht="16.800000000000001" customHeight="1">
       <c r="A89" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B89" s="16">
         <v>26</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D89" s="15">
         <f t="shared" si="10"/>
@@ -5599,7 +5608,7 @@
     </row>
     <row r="90" ht="16.800000000000001" customHeight="1">
       <c r="A90" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B90" s="10"/>
       <c r="C90" s="11"/>
@@ -5610,7 +5619,7 @@
     </row>
     <row r="91" ht="16.800000000000001" customHeight="1">
       <c r="A91" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B91" s="10"/>
       <c r="C91" s="11"/>
@@ -5621,7 +5630,7 @@
     </row>
     <row r="92" ht="16.800000000000001" customHeight="1">
       <c r="A92" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B92" s="10"/>
       <c r="C92" s="11"/>
@@ -5632,7 +5641,7 @@
     </row>
     <row r="93" ht="16.800000000000001" customHeight="1">
       <c r="A93" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B93" s="13"/>
       <c r="C93" s="14"/>
@@ -5643,13 +5652,13 @@
     </row>
     <row r="94" ht="16.800000000000001" customHeight="1">
       <c r="A94" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B94" s="16">
         <v>27</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D94" s="15">
         <f t="shared" si="10"/>
@@ -5658,7 +5667,7 @@
     </row>
     <row r="95" ht="16.800000000000001" customHeight="1">
       <c r="A95" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B95" s="10"/>
       <c r="C95" s="24"/>
@@ -5669,7 +5678,7 @@
     </row>
     <row r="96" ht="16.800000000000001" customHeight="1">
       <c r="A96" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B96" s="10"/>
       <c r="C96" s="24"/>
@@ -5680,7 +5689,7 @@
     </row>
     <row r="97" ht="16.800000000000001" customHeight="1">
       <c r="A97" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B97" s="13"/>
       <c r="C97" s="9"/>
@@ -5691,13 +5700,13 @@
     </row>
     <row r="98" ht="16.800000000000001" customHeight="1">
       <c r="A98" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B98" s="16">
         <v>28</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D98" s="15">
         <f t="shared" si="10"/>
@@ -5706,7 +5715,7 @@
     </row>
     <row r="99" ht="16.800000000000001" customHeight="1">
       <c r="A99" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B99" s="10"/>
       <c r="C99" s="24"/>
@@ -5717,7 +5726,7 @@
     </row>
     <row r="100" ht="16.800000000000001" customHeight="1">
       <c r="A100" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B100" s="10"/>
       <c r="C100" s="24"/>
@@ -5728,7 +5737,7 @@
     </row>
     <row r="101" ht="16.800000000000001" customHeight="1">
       <c r="A101" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B101" s="10"/>
       <c r="C101" s="24"/>
@@ -5739,7 +5748,7 @@
     </row>
     <row r="102" ht="16.800000000000001" customHeight="1">
       <c r="A102" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B102" s="13"/>
       <c r="C102" s="9"/>
@@ -5750,13 +5759,13 @@
     </row>
     <row r="103" ht="16.800000000000001" customHeight="1">
       <c r="A103" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B103" s="16">
         <v>29</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D103" s="15">
         <f t="shared" si="11"/>
@@ -5765,7 +5774,7 @@
     </row>
     <row r="104" ht="16.800000000000001" customHeight="1">
       <c r="A104" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B104" s="10"/>
       <c r="C104" s="24"/>
@@ -5776,7 +5785,7 @@
     </row>
     <row r="105" ht="16.800000000000001" customHeight="1">
       <c r="A105" s="19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B105" s="13"/>
       <c r="C105" s="9"/>
@@ -5787,13 +5796,13 @@
     </row>
     <row r="106" ht="16.800000000000001" customHeight="1">
       <c r="A106" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B106" s="16">
         <v>30</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D106" s="15">
         <f t="shared" si="11"/>
@@ -5802,7 +5811,7 @@
     </row>
     <row r="107" ht="16.800000000000001" customHeight="1">
       <c r="A107" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B107" s="10"/>
       <c r="C107" s="24"/>
@@ -5813,7 +5822,7 @@
     </row>
     <row r="108" ht="16.800000000000001" customHeight="1">
       <c r="A108" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B108" s="10"/>
       <c r="C108" s="24"/>
@@ -5824,7 +5833,7 @@
     </row>
     <row r="109" ht="16.800000000000001" customHeight="1">
       <c r="A109" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B109" s="10"/>
       <c r="C109" s="24"/>
@@ -5835,7 +5844,7 @@
     </row>
     <row r="110" ht="16.800000000000001" customHeight="1">
       <c r="A110" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B110" s="13"/>
       <c r="C110" s="9"/>
@@ -5846,13 +5855,13 @@
     </row>
     <row r="111" ht="16.800000000000001" customHeight="1">
       <c r="A111" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B111" s="16">
         <v>31</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D111" s="15">
         <f t="shared" si="11"/>
@@ -5861,7 +5870,7 @@
     </row>
     <row r="112" ht="16.800000000000001" customHeight="1">
       <c r="A112" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B112" s="13"/>
       <c r="C112" s="9"/>
@@ -5872,13 +5881,13 @@
     </row>
     <row r="113" ht="16.800000000000001" customHeight="1">
       <c r="A113" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B113" s="22">
         <v>32</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D113" s="15">
         <f t="shared" si="11"/>
@@ -5887,13 +5896,13 @@
     </row>
     <row r="114" ht="16.800000000000001" customHeight="1">
       <c r="A114" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B114" s="16">
         <v>33</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D114" s="15">
         <f t="shared" si="11"/>
@@ -5902,7 +5911,7 @@
     </row>
     <row r="115" ht="16.800000000000001" customHeight="1">
       <c r="A115" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B115" s="13"/>
       <c r="C115" s="9"/>
@@ -5913,13 +5922,13 @@
     </row>
     <row r="116" ht="16.800000000000001" customHeight="1">
       <c r="A116" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B116" s="16">
         <v>34</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D116" s="15">
         <f t="shared" si="11"/>
@@ -5928,7 +5937,7 @@
     </row>
     <row r="117" ht="16.800000000000001" customHeight="1">
       <c r="A117" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B117" s="13"/>
       <c r="C117" s="9"/>
@@ -5939,13 +5948,13 @@
     </row>
     <row r="118" ht="16.800000000000001" customHeight="1">
       <c r="A118" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B118" s="16">
         <v>35</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D118" s="15">
         <f t="shared" si="11"/>
@@ -5954,7 +5963,7 @@
     </row>
     <row r="119" ht="16.800000000000001" customHeight="1">
       <c r="A119" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B119" s="10"/>
       <c r="C119" s="24"/>
@@ -5965,7 +5974,7 @@
     </row>
     <row r="120" ht="16.800000000000001" customHeight="1">
       <c r="A120" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B120" s="10"/>
       <c r="C120" s="24"/>
@@ -5976,7 +5985,7 @@
     </row>
     <row r="121" ht="16.800000000000001" customHeight="1">
       <c r="A121" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B121" s="13"/>
       <c r="C121" s="9"/>
@@ -5987,13 +5996,13 @@
     </row>
     <row r="122" ht="16.800000000000001" customHeight="1">
       <c r="A122" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B122" s="16">
         <v>36</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D122" s="15">
         <f t="shared" si="11"/>
@@ -6002,7 +6011,7 @@
     </row>
     <row r="123" ht="16.800000000000001" customHeight="1">
       <c r="A123" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B123" s="10"/>
       <c r="C123" s="24"/>
@@ -6013,7 +6022,7 @@
     </row>
     <row r="124" ht="16.800000000000001" customHeight="1">
       <c r="A124" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B124" s="13"/>
       <c r="C124" s="9"/>
@@ -6024,13 +6033,13 @@
     </row>
     <row r="125" ht="16.800000000000001" customHeight="1">
       <c r="A125" s="25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B125" s="22">
         <v>37</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D125" s="15">
         <f t="shared" si="11"/>
@@ -6039,13 +6048,13 @@
     </row>
     <row r="126" ht="16.800000000000001" customHeight="1">
       <c r="A126" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B126" s="16">
         <v>38</v>
       </c>
       <c r="C126" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D126" s="15">
         <f t="shared" si="11"/>
@@ -6054,7 +6063,7 @@
     </row>
     <row r="127" ht="16.800000000000001" customHeight="1">
       <c r="A127" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B127" s="10"/>
       <c r="C127" s="11"/>
@@ -6065,7 +6074,7 @@
     </row>
     <row r="128" ht="16.800000000000001" customHeight="1">
       <c r="A128" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B128" s="13"/>
       <c r="C128" s="14"/>
@@ -6076,13 +6085,13 @@
     </row>
     <row r="129" ht="16.800000000000001" customHeight="1">
       <c r="A129" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B129" s="16">
         <v>39</v>
       </c>
       <c r="C129" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D129" s="15">
         <f t="shared" si="11"/>
@@ -6091,7 +6100,7 @@
     </row>
     <row r="130" ht="16.800000000000001" customHeight="1">
       <c r="A130" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B130" s="10"/>
       <c r="C130" s="11"/>
@@ -6102,7 +6111,7 @@
     </row>
     <row r="131" ht="16.800000000000001" customHeight="1">
       <c r="A131" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B131" s="13"/>
       <c r="C131" s="14"/>
@@ -6113,13 +6122,13 @@
     </row>
     <row r="132" ht="16.800000000000001" customHeight="1">
       <c r="A132" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B132" s="16">
         <v>40</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D132" s="15">
         <f t="shared" si="11"/>
@@ -6128,7 +6137,7 @@
     </row>
     <row r="133" ht="16.800000000000001" customHeight="1">
       <c r="A133" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B133" s="13"/>
       <c r="C133" s="18"/>
@@ -6139,13 +6148,13 @@
     </row>
     <row r="134" ht="16.800000000000001" customHeight="1">
       <c r="A134" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B134" s="16">
         <v>41</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D134" s="15">
         <f t="shared" si="11"/>
@@ -6154,7 +6163,7 @@
     </row>
     <row r="135" ht="16.800000000000001" customHeight="1">
       <c r="A135" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B135" s="10"/>
       <c r="C135" s="11"/>
@@ -6165,7 +6174,7 @@
     </row>
     <row r="136" ht="16.800000000000001" customHeight="1">
       <c r="A136" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B136" s="13"/>
       <c r="C136" s="14"/>
@@ -6176,13 +6185,13 @@
     </row>
     <row r="137" ht="16.800000000000001" customHeight="1">
       <c r="A137" s="25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B137" s="22">
         <v>42</v>
       </c>
       <c r="C137" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D137" s="15">
         <f t="shared" si="11"/>
@@ -6287,10 +6296,10 @@
     <row r="1">
       <c r="A1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1">
         <v>1</v>
@@ -6413,7 +6422,7 @@
         <v>40</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW1" s="1">
         <v>1</v>
@@ -6540,7 +6549,7 @@
       <c r="A2" s="1"/>
       <c r="C2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -6583,7 +6592,7 @@
       <c r="AT2" s="1"/>
       <c r="AU2" s="1"/>
       <c r="AV2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
@@ -6628,25 +6637,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H3" s="6">
         <f>COUNTIF(H4:H45,"&gt;=2")</f>
@@ -6977,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="6">
         <f t="shared" ref="C4:C9" si="12">COUNTIF($H4:$AU4,"=0")</f>
@@ -7083,7 +7092,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="6">
         <f t="shared" si="12"/>
@@ -7189,7 +7198,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="6">
         <f t="shared" si="12"/>
@@ -7295,7 +7304,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="6">
         <f t="shared" si="12"/>
@@ -7401,7 +7410,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6">
         <f t="shared" si="12"/>
@@ -7507,7 +7516,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="6">
         <f t="shared" si="12"/>
@@ -7613,7 +7622,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="6">
         <f t="shared" ref="C10:C45" si="16">COUNTIF($H10:$AU10,"=0")</f>
@@ -7719,7 +7728,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="6">
         <f t="shared" si="16"/>
@@ -7825,7 +7834,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="6">
         <f t="shared" si="16"/>
@@ -7931,7 +7940,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="6">
         <f t="shared" si="16"/>
@@ -8037,7 +8046,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" s="6">
         <f t="shared" si="16"/>
@@ -8143,7 +8152,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6">
         <f t="shared" si="16"/>
@@ -8249,7 +8258,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="6">
         <f t="shared" si="16"/>
@@ -8355,7 +8364,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C17" s="6">
         <f t="shared" si="16"/>
@@ -8461,7 +8470,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="6">
         <f t="shared" si="16"/>
@@ -8567,7 +8576,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="6">
         <f t="shared" si="16"/>
@@ -8673,7 +8682,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="6">
         <f t="shared" si="16"/>
@@ -8779,7 +8788,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" s="6">
         <f t="shared" si="16"/>
@@ -8885,7 +8894,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C22" s="6">
         <f t="shared" si="16"/>
@@ -8991,7 +9000,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="6">
         <f t="shared" si="16"/>
@@ -9097,7 +9106,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24" s="6">
         <f t="shared" si="16"/>
@@ -9203,7 +9212,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="6">
         <f t="shared" si="16"/>
@@ -9309,7 +9318,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" s="6">
         <f t="shared" si="16"/>
@@ -9415,7 +9424,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C27" s="6">
         <f t="shared" si="16"/>
@@ -9521,7 +9530,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" s="6">
         <f t="shared" si="16"/>
@@ -9627,7 +9636,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C29" s="6">
         <f t="shared" si="16"/>
@@ -9733,7 +9742,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" s="6">
         <f t="shared" si="16"/>
@@ -9839,7 +9848,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="6">
         <f t="shared" si="16"/>
@@ -9945,7 +9954,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" s="6">
         <f t="shared" si="16"/>
@@ -10051,7 +10060,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="6">
         <f t="shared" si="16"/>
@@ -10157,7 +10166,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="6">
         <f t="shared" si="16"/>
@@ -10263,7 +10272,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="6">
         <f t="shared" si="16"/>
@@ -10369,7 +10378,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="6">
         <f t="shared" si="16"/>
@@ -10475,7 +10484,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="6">
         <f t="shared" si="16"/>
@@ -10581,7 +10590,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="6">
         <f t="shared" si="16"/>
@@ -10687,7 +10696,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="6">
         <f t="shared" si="16"/>
@@ -10793,7 +10802,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="6">
         <f t="shared" si="16"/>
@@ -10899,7 +10908,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" s="6">
         <f t="shared" si="16"/>
@@ -11005,7 +11014,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C42" s="6">
         <f t="shared" si="16"/>
@@ -11111,7 +11120,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C43" s="6">
         <f t="shared" si="16"/>
@@ -11217,7 +11226,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C44" s="6">
         <f t="shared" si="16"/>
@@ -11323,7 +11332,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C45" s="6">
         <f t="shared" si="16"/>
@@ -11433,7 +11442,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="4" operator="equal" id="{00A300A4-00C3-4CB7-9C5B-00940024008E}">
+          <x14:cfRule type="expression" priority="4" operator="equal" id="{00AB00D1-00BD-4C4F-95F3-004500EF0053}">
             <xm:f>H4=0</xm:f>
             <x14:dxf>
               <font>
@@ -11450,7 +11459,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="3" operator="equal" id="{00E7003D-009D-4723-9842-006E008700B3}">
+          <x14:cfRule type="expression" priority="3" operator="equal" id="{003B0080-000E-40DB-819A-00D4006F0051}">
             <xm:f>H4=1</xm:f>
             <x14:dxf>
               <font>
@@ -11467,7 +11476,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" operator="equal" id="{00FD0016-00C2-491D-BEFB-0074007D0039}">
+          <x14:cfRule type="expression" priority="2" operator="equal" id="{00DB00D1-00D5-4407-9359-0097001F0046}">
             <xm:f>H4=2</xm:f>
             <x14:dxf>
               <font>
@@ -11484,7 +11493,7 @@
           <xm:sqref>H4:AU45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" operator="equal" id="{000E00A3-0038-4ECD-894D-008C0039008F}">
+          <x14:cfRule type="expression" priority="1" operator="equal" id="{000F006C-0059-423A-B7E1-007E00840030}">
             <xm:f>H4=3</xm:f>
             <x14:dxf>
               <font>
@@ -11516,7 +11525,7 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1">
         <v>1</v>
@@ -11641,7 +11650,7 @@
     </row>
     <row r="2" ht="14.25">
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -11686,13 +11695,13 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -11740,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -11789,7 +11798,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -11838,7 +11847,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -11887,7 +11896,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -11936,7 +11945,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -11985,7 +11994,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -12034,7 +12043,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -12083,7 +12092,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -12132,7 +12141,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -12181,7 +12190,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -12230,7 +12239,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -12279,7 +12288,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -12328,7 +12337,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -12377,7 +12386,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -12426,7 +12435,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -12475,7 +12484,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -12524,7 +12533,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -12573,7 +12582,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -12622,7 +12631,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -12671,7 +12680,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -12720,7 +12729,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -12769,7 +12778,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -12818,7 +12827,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -12867,7 +12876,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -12916,7 +12925,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -12965,7 +12974,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -13014,7 +13023,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -13063,7 +13072,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -13112,7 +13121,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -13161,7 +13170,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
@@ -13210,7 +13219,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -13259,7 +13268,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -13308,7 +13317,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
@@ -13357,7 +13366,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -13406,7 +13415,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -13455,7 +13464,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
@@ -13504,7 +13513,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
@@ -13553,7 +13562,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
@@ -13602,7 +13611,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
@@ -13651,7 +13660,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
@@ -13700,7 +13709,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
@@ -13749,7 +13758,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
@@ -13795,13 +13804,13 @@
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" ht="14.25">
@@ -13809,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C48" s="6"/>
     </row>
@@ -13818,7 +13827,7 @@
         <v>2</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C49" s="6"/>
     </row>
@@ -13827,7 +13836,7 @@
         <v>3</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C50" s="6"/>
     </row>
@@ -13836,7 +13845,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C51" s="6"/>
     </row>
@@ -13845,7 +13854,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="6"/>
     </row>
@@ -13854,7 +13863,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C53" s="6"/>
     </row>
@@ -13863,7 +13872,7 @@
         <v>7</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C54" s="6"/>
     </row>
@@ -13872,7 +13881,7 @@
         <v>8</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C55" s="6"/>
     </row>
@@ -13881,7 +13890,7 @@
         <v>9</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C56" s="6"/>
     </row>
@@ -13890,7 +13899,7 @@
         <v>10</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C57" s="6"/>
     </row>
@@ -13899,7 +13908,7 @@
         <v>11</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C58" s="6"/>
     </row>
@@ -13908,7 +13917,7 @@
         <v>12</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C59" s="6"/>
     </row>
@@ -13917,7 +13926,7 @@
         <v>13</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C60" s="6"/>
     </row>
@@ -13926,7 +13935,7 @@
         <v>14</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C61" s="6"/>
     </row>
@@ -13935,7 +13944,7 @@
         <v>15</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C62" s="6"/>
     </row>
@@ -13944,7 +13953,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C63" s="6"/>
     </row>
@@ -13953,7 +13962,7 @@
         <v>17</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C64" s="6"/>
     </row>
@@ -13962,7 +13971,7 @@
         <v>18</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C65" s="6"/>
     </row>
@@ -13971,7 +13980,7 @@
         <v>19</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C66" s="6"/>
     </row>
@@ -13980,7 +13989,7 @@
         <v>20</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="6"/>
     </row>
@@ -13989,7 +13998,7 @@
         <v>21</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C68" s="6"/>
     </row>
@@ -13998,7 +14007,7 @@
         <v>22</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C69" s="6"/>
     </row>
@@ -14007,7 +14016,7 @@
         <v>23</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C70" s="6"/>
     </row>
@@ -14016,7 +14025,7 @@
         <v>24</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C71" s="6"/>
     </row>
@@ -14025,7 +14034,7 @@
         <v>25</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C72" s="6"/>
     </row>
@@ -14034,7 +14043,7 @@
         <v>26</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C73" s="6"/>
     </row>
@@ -14043,7 +14052,7 @@
         <v>27</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C74" s="6"/>
     </row>
@@ -14052,7 +14061,7 @@
         <v>28</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C75" s="6"/>
     </row>
@@ -14061,7 +14070,7 @@
         <v>29</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C76" s="6"/>
     </row>
@@ -14070,7 +14079,7 @@
         <v>30</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C77" s="6"/>
     </row>
@@ -14079,7 +14088,7 @@
         <v>31</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C78" s="6"/>
     </row>
@@ -14088,7 +14097,7 @@
         <v>32</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C79" s="6"/>
     </row>
@@ -14097,7 +14106,7 @@
         <v>33</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C80" s="6"/>
     </row>
@@ -14106,7 +14115,7 @@
         <v>34</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C81" s="6"/>
     </row>
@@ -14115,7 +14124,7 @@
         <v>35</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C82" s="6"/>
     </row>
@@ -14124,7 +14133,7 @@
         <v>36</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C83" s="6"/>
     </row>
@@ -14133,7 +14142,7 @@
         <v>37</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C84" s="6"/>
     </row>
@@ -14142,7 +14151,7 @@
         <v>38</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C85" s="6"/>
     </row>
@@ -14151,7 +14160,7 @@
         <v>39</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C86" s="6"/>
     </row>
@@ -14160,7 +14169,7 @@
         <v>40</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C87" s="6"/>
     </row>
@@ -14169,7 +14178,7 @@
         <v>41</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C88" s="6"/>
     </row>
@@ -14178,19 +14187,19 @@
         <v>42</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C89" s="6"/>
     </row>
     <row r="91" ht="14.25">
       <c r="A91" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="92" ht="14.25">
@@ -14198,7 +14207,7 @@
         <v>1</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C92" s="6"/>
     </row>
@@ -14207,7 +14216,7 @@
         <v>2</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C93" s="6"/>
     </row>
@@ -14216,7 +14225,7 @@
         <v>3</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C94" s="6"/>
     </row>
@@ -14225,7 +14234,7 @@
         <v>4</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C95" s="6"/>
     </row>
@@ -14234,7 +14243,7 @@
         <v>5</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C96" s="6"/>
     </row>
@@ -14243,7 +14252,7 @@
         <v>6</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C97" s="6"/>
     </row>
@@ -14252,7 +14261,7 @@
         <v>7</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C98" s="6"/>
     </row>
@@ -14261,7 +14270,7 @@
         <v>8</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C99" s="6"/>
     </row>
@@ -14270,7 +14279,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C100" s="6"/>
     </row>
@@ -14279,7 +14288,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C101" s="6"/>
     </row>
@@ -14288,7 +14297,7 @@
         <v>11</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C102" s="6"/>
     </row>
@@ -14297,7 +14306,7 @@
         <v>12</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C103" s="6"/>
     </row>
@@ -14306,7 +14315,7 @@
         <v>13</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C104" s="6"/>
     </row>
@@ -14315,7 +14324,7 @@
         <v>14</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C105" s="6"/>
     </row>
@@ -14324,7 +14333,7 @@
         <v>15</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C106" s="6"/>
     </row>
@@ -14333,7 +14342,7 @@
         <v>16</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C107" s="6"/>
     </row>
@@ -14342,7 +14351,7 @@
         <v>17</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C108" s="6"/>
     </row>
@@ -14351,7 +14360,7 @@
         <v>18</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C109" s="6"/>
     </row>
@@ -14360,7 +14369,7 @@
         <v>19</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C110" s="6"/>
     </row>
@@ -14369,7 +14378,7 @@
         <v>20</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C111" s="6"/>
     </row>
@@ -14378,7 +14387,7 @@
         <v>21</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C112" s="6"/>
     </row>
@@ -14387,7 +14396,7 @@
         <v>22</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C113" s="6"/>
     </row>
@@ -14396,7 +14405,7 @@
         <v>23</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C114" s="6"/>
     </row>
@@ -14405,7 +14414,7 @@
         <v>24</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C115" s="6"/>
     </row>
@@ -14414,7 +14423,7 @@
         <v>25</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C116" s="6"/>
     </row>
@@ -14423,7 +14432,7 @@
         <v>26</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C117" s="6"/>
     </row>
@@ -14432,7 +14441,7 @@
         <v>27</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C118" s="6"/>
     </row>
@@ -14441,7 +14450,7 @@
         <v>28</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C119" s="6"/>
     </row>
@@ -14450,7 +14459,7 @@
         <v>29</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C120" s="6"/>
     </row>
@@ -14459,7 +14468,7 @@
         <v>30</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C121" s="6"/>
     </row>
@@ -14468,7 +14477,7 @@
         <v>31</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C122" s="6"/>
     </row>
@@ -14477,7 +14486,7 @@
         <v>32</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C123" s="6"/>
     </row>
@@ -14486,7 +14495,7 @@
         <v>33</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C124" s="6"/>
     </row>
@@ -14495,7 +14504,7 @@
         <v>34</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C125" s="6"/>
     </row>
@@ -14504,7 +14513,7 @@
         <v>35</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C126" s="6"/>
     </row>
@@ -14513,7 +14522,7 @@
         <v>36</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C127" s="6"/>
     </row>
@@ -14522,7 +14531,7 @@
         <v>37</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C128" s="6"/>
     </row>
@@ -14531,7 +14540,7 @@
         <v>38</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C129" s="6"/>
     </row>
@@ -14540,7 +14549,7 @@
         <v>39</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C130" s="6"/>
     </row>
@@ -14549,7 +14558,7 @@
         <v>40</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C131" s="6"/>
     </row>
@@ -14558,7 +14567,7 @@
         <v>41</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C132" s="6"/>
     </row>
@@ -14567,19 +14576,19 @@
         <v>42</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C133" s="6"/>
     </row>
     <row r="135" ht="14.25">
       <c r="A135" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="136" ht="14.25">
@@ -14587,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C136" s="6"/>
     </row>
@@ -14596,7 +14605,7 @@
         <v>2</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C137" s="6"/>
     </row>
@@ -14605,7 +14614,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C138" s="6"/>
     </row>
@@ -14614,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C139" s="6"/>
     </row>
@@ -14623,7 +14632,7 @@
         <v>5</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C140" s="6"/>
     </row>
@@ -14632,7 +14641,7 @@
         <v>6</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C141" s="6"/>
     </row>
@@ -14641,7 +14650,7 @@
         <v>7</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C142" s="6"/>
     </row>
@@ -14650,7 +14659,7 @@
         <v>8</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C143" s="6"/>
     </row>
@@ -14659,7 +14668,7 @@
         <v>9</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C144" s="6"/>
     </row>
@@ -14668,7 +14677,7 @@
         <v>10</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C145" s="6"/>
     </row>
@@ -14677,7 +14686,7 @@
         <v>11</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C146" s="6"/>
     </row>
@@ -14686,7 +14695,7 @@
         <v>12</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C147" s="6"/>
     </row>
@@ -14695,7 +14704,7 @@
         <v>13</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C148" s="6"/>
     </row>
@@ -14704,7 +14713,7 @@
         <v>14</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C149" s="6"/>
     </row>
@@ -14713,7 +14722,7 @@
         <v>15</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C150" s="6"/>
     </row>
@@ -14722,7 +14731,7 @@
         <v>16</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C151" s="6"/>
     </row>
@@ -14731,7 +14740,7 @@
         <v>17</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C152" s="6"/>
     </row>
@@ -14740,7 +14749,7 @@
         <v>18</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C153" s="6"/>
     </row>
@@ -14749,7 +14758,7 @@
         <v>19</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C154" s="6"/>
     </row>
@@ -14758,7 +14767,7 @@
         <v>20</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C155" s="6"/>
     </row>
@@ -14767,7 +14776,7 @@
         <v>21</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C156" s="6"/>
     </row>
@@ -14776,7 +14785,7 @@
         <v>22</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C157" s="6"/>
     </row>
@@ -14785,7 +14794,7 @@
         <v>23</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C158" s="6"/>
     </row>
@@ -14794,7 +14803,7 @@
         <v>24</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C159" s="6"/>
     </row>
@@ -14803,7 +14812,7 @@
         <v>25</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C160" s="6"/>
     </row>
@@ -14812,7 +14821,7 @@
         <v>26</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C161" s="6"/>
     </row>
@@ -14821,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C162" s="6"/>
     </row>
@@ -14830,7 +14839,7 @@
         <v>28</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C163" s="6"/>
     </row>
@@ -14839,7 +14848,7 @@
         <v>29</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C164" s="6"/>
     </row>
@@ -14848,7 +14857,7 @@
         <v>30</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C165" s="6"/>
     </row>
@@ -14857,7 +14866,7 @@
         <v>31</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C166" s="6"/>
     </row>
@@ -14866,7 +14875,7 @@
         <v>32</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C167" s="6"/>
     </row>
@@ -14875,7 +14884,7 @@
         <v>33</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C168" s="6"/>
     </row>
@@ -14884,7 +14893,7 @@
         <v>34</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C169" s="6"/>
     </row>
@@ -14893,7 +14902,7 @@
         <v>35</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C170" s="6"/>
     </row>
@@ -14902,7 +14911,7 @@
         <v>36</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C171" s="6"/>
     </row>
@@ -14911,7 +14920,7 @@
         <v>37</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C172" s="6"/>
     </row>
@@ -14920,7 +14929,7 @@
         <v>38</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C173" s="6"/>
     </row>
@@ -14929,7 +14938,7 @@
         <v>39</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C174" s="6"/>
     </row>
@@ -14938,7 +14947,7 @@
         <v>40</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C175" s="6"/>
     </row>
@@ -14947,7 +14956,7 @@
         <v>41</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C176" s="6"/>
     </row>
@@ -14956,19 +14965,19 @@
         <v>42</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C177" s="6"/>
     </row>
     <row r="179" ht="14.25">
       <c r="A179" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="180" ht="14.25">
@@ -14976,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C180" s="6"/>
     </row>
@@ -14985,7 +14994,7 @@
         <v>2</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C181" s="6"/>
     </row>
@@ -14994,7 +15003,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C182" s="6"/>
     </row>
@@ -15003,7 +15012,7 @@
         <v>4</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C183" s="6"/>
     </row>
@@ -15012,7 +15021,7 @@
         <v>5</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C184" s="6"/>
     </row>
@@ -15021,7 +15030,7 @@
         <v>6</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C185" s="6"/>
     </row>
@@ -15030,7 +15039,7 @@
         <v>7</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C186" s="6"/>
     </row>
@@ -15039,7 +15048,7 @@
         <v>8</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C187" s="6"/>
     </row>
@@ -15048,7 +15057,7 @@
         <v>9</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C188" s="6"/>
     </row>
@@ -15057,7 +15066,7 @@
         <v>10</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C189" s="6"/>
     </row>
@@ -15066,7 +15075,7 @@
         <v>11</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C190" s="6"/>
     </row>
@@ -15075,7 +15084,7 @@
         <v>12</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C191" s="6"/>
     </row>
@@ -15084,7 +15093,7 @@
         <v>13</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C192" s="6"/>
     </row>
@@ -15093,7 +15102,7 @@
         <v>14</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C193" s="6"/>
     </row>
@@ -15102,7 +15111,7 @@
         <v>15</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C194" s="6"/>
     </row>
@@ -15111,7 +15120,7 @@
         <v>16</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C195" s="6"/>
     </row>
@@ -15120,7 +15129,7 @@
         <v>17</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C196" s="6"/>
     </row>
@@ -15129,7 +15138,7 @@
         <v>18</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C197" s="6"/>
     </row>
@@ -15138,7 +15147,7 @@
         <v>19</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C198" s="6"/>
     </row>
@@ -15147,7 +15156,7 @@
         <v>20</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C199" s="6"/>
     </row>
@@ -15156,7 +15165,7 @@
         <v>21</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C200" s="6"/>
     </row>
@@ -15165,7 +15174,7 @@
         <v>22</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C201" s="6"/>
     </row>
@@ -15174,7 +15183,7 @@
         <v>23</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C202" s="6"/>
     </row>
@@ -15183,7 +15192,7 @@
         <v>24</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C203" s="6"/>
     </row>
@@ -15192,7 +15201,7 @@
         <v>25</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C204" s="6"/>
     </row>
@@ -15201,7 +15210,7 @@
         <v>26</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C205" s="6"/>
     </row>
@@ -15210,7 +15219,7 @@
         <v>27</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C206" s="6"/>
     </row>
@@ -15219,7 +15228,7 @@
         <v>28</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C207" s="6"/>
     </row>
@@ -15228,7 +15237,7 @@
         <v>29</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C208" s="6"/>
     </row>
@@ -15237,7 +15246,7 @@
         <v>30</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C209" s="6"/>
     </row>
@@ -15246,7 +15255,7 @@
         <v>31</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C210" s="6"/>
     </row>
@@ -15255,7 +15264,7 @@
         <v>32</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C211" s="6"/>
     </row>
@@ -15264,7 +15273,7 @@
         <v>33</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C212" s="6"/>
     </row>
@@ -15273,7 +15282,7 @@
         <v>34</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C213" s="6"/>
     </row>
@@ -15282,7 +15291,7 @@
         <v>35</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C214" s="6"/>
     </row>
@@ -15291,7 +15300,7 @@
         <v>36</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C215" s="6"/>
     </row>
@@ -15300,7 +15309,7 @@
         <v>37</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C216" s="6"/>
     </row>
@@ -15309,7 +15318,7 @@
         <v>38</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C217" s="6"/>
     </row>
@@ -15318,7 +15327,7 @@
         <v>39</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C218" s="6"/>
     </row>
@@ -15327,7 +15336,7 @@
         <v>40</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C219" s="6"/>
     </row>
@@ -15336,7 +15345,7 @@
         <v>41</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C220" s="6"/>
     </row>
@@ -15345,7 +15354,7 @@
         <v>42</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C221" s="6"/>
     </row>
@@ -15367,34 +15376,34 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
